--- a/data/manual_annotations.xlsx
+++ b/data/manual_annotations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rajika Rajesh\Downloads\Thesis-Datalake\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C826CCD-8AAF-4008-8158-D31973A4C032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEFA1896-C4C7-4A9A-AB85-46272D0A7667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D2BB9688-6256-4F5B-808F-A4F653635EB6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="207">
   <si>
     <t>Colonna</t>
   </si>
@@ -87,39 +87,319 @@
     <t>Type of offender–victim relationship (Affective, Family, Work, etc.)</t>
   </si>
   <si>
+    <t>Example 1</t>
+  </si>
+  <si>
     <t>Messina</t>
   </si>
   <si>
+    <t>27158/2022</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
     <t>NA</t>
   </si>
   <si>
+    <t>Minisi Antonio</t>
+  </si>
+  <si>
     <t>Court of Cassation</t>
   </si>
   <si>
     <t>condonna</t>
   </si>
   <si>
+    <t>Art. 572,
+ Art. 81,582</t>
+  </si>
+  <si>
     <t>Male</t>
   </si>
   <si>
     <t>Italy</t>
   </si>
   <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>Affetivo</t>
+  </si>
+  <si>
+    <t>Convivente</t>
+  </si>
+  <si>
+    <t>20230116_snpen@s60@a2023@n01302@tS@oY</t>
+  </si>
+  <si>
+    <t>Example 2</t>
+  </si>
+  <si>
+    <t>Milan</t>
+  </si>
+  <si>
+    <t>31300/22</t>
+  </si>
+  <si>
+    <t>Kristina Karabush</t>
+  </si>
+  <si>
+    <t>Boicu Daniel</t>
+  </si>
+  <si>
+    <t>2 agosto 2022</t>
+  </si>
+  <si>
+    <t>23 novembre 2022</t>
+  </si>
+  <si>
+    <t>Condonna</t>
+  </si>
+  <si>
+    <t>Art.572, Art.61</t>
+  </si>
+  <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>milan</t>
+  </si>
+  <si>
+    <t>BIANCHE (knife)</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>Spouse</t>
+  </si>
+  <si>
+    <t>20230117_snpen@s60@a2023@n01652@tS@oY</t>
+  </si>
+  <si>
+    <t>Example 3</t>
+  </si>
+  <si>
+    <t>Cremona</t>
+  </si>
+  <si>
+    <t>29514/2025</t>
+  </si>
+  <si>
+    <t>Farhia Gedi Adan, 
+Marie Bernard Rolleau,
+Giuseppina Agosti,
+ Mattia De Pinto</t>
+  </si>
+  <si>
+    <t>SAIDI ABDEL MOUME</t>
+  </si>
+  <si>
+    <t>Art.444</t>
+  </si>
+  <si>
     <t>Tunisia</t>
   </si>
   <si>
+    <t>cremona</t>
+  </si>
+  <si>
+    <t>home?</t>
+  </si>
+  <si>
+    <t>DA LANCIO (throwing waepon)</t>
+  </si>
+  <si>
+    <t>Altro</t>
+  </si>
+  <si>
+    <t>_20251015_snpen@s20@a2025@n33827@tO</t>
+  </si>
+  <si>
+    <t>Example 4</t>
+  </si>
+  <si>
     <t>FIRENZE</t>
   </si>
   <si>
+    <t>13505/2025</t>
+  </si>
+  <si>
+    <t>Gessica Ratti,
+ Kaiss Agengi</t>
+  </si>
+  <si>
+    <t>Art.62</t>
+  </si>
+  <si>
+    <t>Lucca</t>
+  </si>
+  <si>
+    <t>personal injury?
+per il reato di lesione personale</t>
+  </si>
+  <si>
+    <t>_daOscurare_20251023_snpen@s70@a2025@n34554@tO@oY</t>
+  </si>
+  <si>
+    <t>Example 5</t>
+  </si>
+  <si>
+    <t>CATANIA</t>
+  </si>
+  <si>
+    <t>7218/2025</t>
+  </si>
+  <si>
+    <t>LEONARDI ORAZIO,
+DI SALVATORE FRANCESCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art. 674 , Art. 110,
+Art. 612-bis </t>
+  </si>
+  <si>
+    <t>Catania</t>
+  </si>
+  <si>
+    <t>76 - 84</t>
+  </si>
+  <si>
+    <t>_20251003_snpen@s70@a2025@n32627@tO</t>
+  </si>
+  <si>
+    <t>Example 6</t>
+  </si>
+  <si>
+    <t>Napoli</t>
+  </si>
+  <si>
+    <t>9268/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anna Maria Lombardi, Fatima.
+</t>
+  </si>
+  <si>
+    <t>Romagnuolo Giovanni</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Assoluzione</t>
   </si>
   <si>
+    <t xml:space="preserve">Art.572, Art 192
+</t>
+  </si>
+  <si>
+    <t>Sant'Angelo a Scala (AV</t>
+  </si>
+  <si>
+    <t>20250625_snpen@s60@a2025@n23789@tS@oY</t>
+  </si>
+  <si>
+    <t>Example 7</t>
+  </si>
+  <si>
+    <t>Milano</t>
+  </si>
+  <si>
+    <t>3445/24</t>
+  </si>
+  <si>
+    <t>Valery Rocco</t>
+  </si>
+  <si>
+    <t>Dota Andrea</t>
+  </si>
+  <si>
+    <t>Art. 572 , Art. 612-bis,
+ Art. 582,585 , 
+Art. 577</t>
+  </si>
+  <si>
+    <t>20240711_snpen@s60@a2024@n27645@tS@oY</t>
+  </si>
+  <si>
+    <t>Example 8</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>19937/2025</t>
+  </si>
+  <si>
+    <t>Claudio L’Atragna</t>
+  </si>
+  <si>
+    <t>L'Atragna Francesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 14/01/2025</t>
+  </si>
+  <si>
+    <t>artt. 582 e 61</t>
+  </si>
+  <si>
+    <t>Carini</t>
+  </si>
+  <si>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>Example 9</t>
+  </si>
+  <si>
+    <t>BRINDISI</t>
+  </si>
+  <si>
+    <t>21838/2025</t>
+  </si>
+  <si>
+    <t>Leonardo Ciaccia.</t>
+  </si>
+  <si>
+    <t>MILO FRANCESCO</t>
+  </si>
+  <si>
+    <t>Art. 582, 590</t>
+  </si>
+  <si>
+    <t>Brindisi</t>
+  </si>
+  <si>
+    <t>Example 10</t>
+  </si>
+  <si>
+    <t>POTENZA</t>
+  </si>
+  <si>
+    <t>27015/2025</t>
+  </si>
+  <si>
+    <t>DE FAZIO ALFREDO</t>
+  </si>
+  <si>
+    <t>artt. 582-585 e 
+56-629 cod. pen</t>
+  </si>
+  <si>
+    <t>MANDURIA</t>
+  </si>
+  <si>
+    <t>Taranto</t>
+  </si>
+  <si>
     <t>PROCEEDING_ID_RGN</t>
   </si>
   <si>
     <t>CRIME_ARTICLE</t>
   </si>
   <si>
+    <t xml:space="preserve">lover </t>
+  </si>
+  <si>
     <t>VICTIM_OFFENDER_RELATIONSHIP</t>
   </si>
   <si>
@@ -132,7 +412,16 @@
     <t>SUSPECT_ID</t>
   </si>
   <si>
+    <t xml:space="preserve">_20251023_snpen@s70@a2025@n34564@tO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">_daOscurare_20251013_snpen@s50@a2025@n33693@tO@oY </t>
+  </si>
+  <si>
     <t>FILE_NAME</t>
+  </si>
+  <si>
+    <t>_daOscurare_20251015_snpen@s50@a2025@n33859@tS@oY</t>
   </si>
   <si>
     <t>Example 11</t>
@@ -407,7 +696,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -431,6 +720,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -446,7 +742,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -454,12 +750,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -473,8 +782,20 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -794,381 +1115,691 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F57D56E-4B43-4056-8C0B-01BEB090726F}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37.54296875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="19.26953125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="28.6328125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="24.1796875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="29.6328125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20.54296875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25.7265625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="19.1796875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="17.90625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="18.90625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="17.453125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.90625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="25.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="22.54296875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="20.90625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="20.08984375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="26.54296875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="21.08984375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="17.81640625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="19.26953125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="28.6328125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="24.1796875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="29.6328125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="20.54296875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="25.7265625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="19.1796875" style="3" customWidth="1"/>
+    <col min="19" max="19" width="17.90625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="18.90625" style="3" customWidth="1"/>
+    <col min="21" max="21" width="17.453125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:21" ht="17" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>42</v>
+        <v>107</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>52</v>
+      <c r="D2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="K3" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>60</v>
       </c>
+      <c r="R3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>70</v>
+        <v>109</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>72</v>
+        <v>20</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>164</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>18</v>
+        <v>35</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>79</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>175</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="4">
+        <v>44127</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="4">
+        <v>45845</v>
+      </c>
+      <c r="E9" s="4">
+        <v>45729</v>
+      </c>
+      <c r="F9" s="4">
+        <v>45615</v>
+      </c>
+      <c r="G9" s="4">
+        <v>45405</v>
+      </c>
+      <c r="H9" s="4">
+        <v>45225</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="4">
+        <v>45699</v>
+      </c>
+      <c r="K9" s="4">
+        <v>45838</v>
+      </c>
+      <c r="L9" s="4">
         <v>45813</v>
       </c>
-      <c r="C9" s="4">
+      <c r="M9" s="4">
         <v>45685</v>
       </c>
-      <c r="D9" s="4">
+      <c r="N9" s="4">
         <v>45376</v>
       </c>
-      <c r="E9" s="4">
+      <c r="O9" s="4">
         <v>45686</v>
       </c>
-      <c r="F9" s="4">
+      <c r="P9" s="4">
         <v>45573</v>
       </c>
-      <c r="G9" s="4">
+      <c r="Q9" s="4">
         <v>45587</v>
       </c>
-      <c r="H9" s="4">
+      <c r="R9" s="4">
         <v>45705</v>
       </c>
-      <c r="I9" s="4">
+      <c r="S9" s="4">
         <v>45688</v>
       </c>
-      <c r="J9" s="4">
+      <c r="T9" s="4">
         <v>44545</v>
       </c>
-      <c r="K9" s="4">
+      <c r="U9" s="4">
         <v>44959</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="4">
+        <v>44886</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="4">
+        <v>45926</v>
+      </c>
+      <c r="E10" s="4">
         <v>45910</v>
-      </c>
-      <c r="C10" s="4">
-        <v>45918</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="4">
-        <v>45926</v>
       </c>
       <c r="F10" s="4">
         <v>45833</v>
       </c>
       <c r="G10" s="4">
+        <v>45789</v>
+      </c>
+      <c r="H10" s="4">
+        <v>45434</v>
+      </c>
+      <c r="I10" s="4">
+        <v>45925</v>
+      </c>
+      <c r="J10" s="4">
+        <v>45937</v>
+      </c>
+      <c r="K10" s="4">
+        <v>45910</v>
+      </c>
+      <c r="L10" s="4">
+        <v>45910</v>
+      </c>
+      <c r="M10" s="4">
+        <v>45918</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="O10" s="4">
+        <v>45926</v>
+      </c>
+      <c r="P10" s="4">
         <v>45833</v>
       </c>
-      <c r="H10" s="4">
+      <c r="Q10" s="4">
+        <v>45833</v>
+      </c>
+      <c r="R10" s="4">
         <v>45847</v>
       </c>
-      <c r="I10" s="4">
+      <c r="S10" s="4">
         <v>45847</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K10" s="4">
+      <c r="T10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="U10" s="4">
         <v>45184</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="3">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="C11" s="3">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D11" s="3">
         <v>2025</v>
@@ -1183,170 +1814,321 @@
         <v>2025</v>
       </c>
       <c r="H11" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="I11" s="3">
         <v>2025</v>
       </c>
       <c r="J11" s="3">
+        <v>2025</v>
+      </c>
+      <c r="K11" s="3">
+        <v>2025</v>
+      </c>
+      <c r="L11" s="3">
+        <v>2025</v>
+      </c>
+      <c r="M11" s="3">
+        <v>2025</v>
+      </c>
+      <c r="N11" s="3">
+        <v>2025</v>
+      </c>
+      <c r="O11" s="3">
+        <v>2025</v>
+      </c>
+      <c r="P11" s="3">
+        <v>2025</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>2025</v>
+      </c>
+      <c r="R11" s="3">
+        <v>2025</v>
+      </c>
+      <c r="S11" s="3">
+        <v>2025</v>
+      </c>
+      <c r="T11" s="3">
         <v>2023</v>
       </c>
-      <c r="K11" s="3">
+      <c r="U11" s="3">
         <v>2023</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="62" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>20</v>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="290" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" ht="290" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>100</v>
+      <c r="B14" s="6"/>
+      <c r="M14" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>192</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="G15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="J15" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
@@ -1354,104 +2136,194 @@
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="T17" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>18</v>
+      <c r="U17" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="3">
+        <v>43</v>
+      </c>
+      <c r="C18" s="3">
+        <v>33</v>
+      </c>
+      <c r="D18" s="3">
+        <v>19</v>
+      </c>
+      <c r="E18" s="3">
+        <v>41</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="3">
+        <v>65</v>
+      </c>
+      <c r="H18" s="3">
+        <v>36</v>
+      </c>
+      <c r="I18" s="3">
+        <v>54</v>
+      </c>
+      <c r="J18" s="3">
+        <v>35</v>
+      </c>
+      <c r="K18" s="3">
+        <v>36</v>
+      </c>
+      <c r="L18" s="3">
         <v>39</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="P18" s="3">
         <v>36</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="R18" s="3">
         <v>40</v>
       </c>
-      <c r="I18" s="3">
+      <c r="S18" s="3">
         <v>51</v>
       </c>
-      <c r="J18" s="3">
+      <c r="T18" s="3">
         <v>40</v>
       </c>
-      <c r="K18" s="3">
+      <c r="U18" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>14</v>
       </c>
@@ -1459,215 +2331,376 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>18</v>
+      <c r="U20" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>29</v>
+        <v>118</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B25" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>52</v>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L25" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C25" r:id="rId1" xr:uid="{6662672D-66AF-487C-8145-40443E269CA8}"/>
-    <hyperlink ref="D25" r:id="rId2" xr:uid="{7BF1EDFF-F3B9-463D-87A9-D249CBC2A92F}"/>
-    <hyperlink ref="F25" r:id="rId3" xr:uid="{D11022E9-C122-4E8E-AFC2-FACB1517AE28}"/>
-    <hyperlink ref="E25" r:id="rId4" xr:uid="{BEFB4D60-57C0-48AB-B21E-0665C8BFCB12}"/>
-    <hyperlink ref="C2" r:id="rId5" xr:uid="{FF7D931C-507B-4419-809E-DE298A55EB03}"/>
-    <hyperlink ref="D2" r:id="rId6" xr:uid="{95D2A9AB-3616-4E5E-8B0A-07869255F34D}"/>
-    <hyperlink ref="F2" r:id="rId7" xr:uid="{E0CF72A8-CEC2-4B89-8438-7EF47CC285DB}"/>
-    <hyperlink ref="E2" r:id="rId8" xr:uid="{58C07E3F-8ACC-4378-8AC0-3630B4DA6C9E}"/>
+    <hyperlink ref="M25" r:id="rId1" xr:uid="{6662672D-66AF-487C-8145-40443E269CA8}"/>
+    <hyperlink ref="N25" r:id="rId2" xr:uid="{7BF1EDFF-F3B9-463D-87A9-D249CBC2A92F}"/>
+    <hyperlink ref="P25" r:id="rId3" xr:uid="{D11022E9-C122-4E8E-AFC2-FACB1517AE28}"/>
+    <hyperlink ref="O25" r:id="rId4" xr:uid="{BEFB4D60-57C0-48AB-B21E-0665C8BFCB12}"/>
+    <hyperlink ref="M2" r:id="rId5" xr:uid="{FF7D931C-507B-4419-809E-DE298A55EB03}"/>
+    <hyperlink ref="N2" r:id="rId6" xr:uid="{95D2A9AB-3616-4E5E-8B0A-07869255F34D}"/>
+    <hyperlink ref="P2" r:id="rId7" xr:uid="{E0CF72A8-CEC2-4B89-8438-7EF47CC285DB}"/>
+    <hyperlink ref="O2" r:id="rId8" xr:uid="{58C07E3F-8ACC-4378-8AC0-3630B4DA6C9E}"/>
+    <hyperlink ref="L2" r:id="rId9" xr:uid="{7DA5529B-58A4-4C21-A95D-EFA115E95601}"/>
+    <hyperlink ref="B2" r:id="rId10" xr:uid="{B7567B9D-72B2-4B0C-B503-69CD6B7A27DC}"/>
+    <hyperlink ref="C2" r:id="rId11" xr:uid="{68ACE77B-591A-4C61-AFD4-2A56418AE0BF}"/>
+    <hyperlink ref="D2" r:id="rId12" xr:uid="{30BB4126-88BF-4EFF-98C5-E9DEB572D25B}"/>
+    <hyperlink ref="E2" r:id="rId13" xr:uid="{4C9ECD43-1731-4543-9EF7-11107A931588}"/>
+    <hyperlink ref="F2" r:id="rId14" xr:uid="{FC4F19E3-1E90-4D25-870E-61FDFDFDACAE}"/>
+    <hyperlink ref="G2" r:id="rId15" xr:uid="{48086816-5B90-4C73-9AE7-01900057B9E8}"/>
+    <hyperlink ref="H2" r:id="rId16" xr:uid="{4765B58A-301A-4342-8F60-282F4F3F7C24}"/>
+    <hyperlink ref="I2" r:id="rId17" xr:uid="{25F3AE75-B92C-4122-AB35-6D427560E737}"/>
+    <hyperlink ref="J2" r:id="rId18" xr:uid="{AA053DCF-D67D-443E-A50F-D06E617B283F}"/>
+    <hyperlink ref="K2" r:id="rId19" xr:uid="{A49E1CC8-DC75-4797-8979-A74D12772BE5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
